--- a/backtest_runs/20260410_193731/by_symbol/AGP/AGP.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/AGP/AGP.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -538,10 +538,10 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>100000</v>
@@ -630,10 +630,10 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>103393</v>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>103393</v>
@@ -771,7 +771,7 @@
         <v>-276.6600000000006</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>112089.52</v>
@@ -863,7 +863,7 @@
         <v>-4129.019999999999</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>115941.88</v>
@@ -909,7 +909,7 @@
         <v>-5021.639999999988</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>110920.24</v>
@@ -955,7 +955,7 @@
         <v>-527.22000000001</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>110393.02</v>
@@ -1044,10 +1044,10 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>110393.02</v>
@@ -1185,7 +1185,7 @@
         <v>-7370.640000000002</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>103450.42</v>
@@ -1231,7 +1231,7 @@
         <v>-31.32000000000119</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>103419.1</v>
@@ -1277,7 +1277,7 @@
         <v>-2103.660000000001</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>101315.44</v>
@@ -1323,7 +1323,7 @@
         <v>-2902.319999999987</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" s="3" t="n">
         <v>98413.12000000001</v>
@@ -1415,7 +1415,7 @@
         <v>-3043.260000000007</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>99906.03999999999</v>
@@ -1461,7 +1461,7 @@
         <v>-2448.179999999999</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>97457.86</v>
